--- a/overtime/sample/5월 초과근무수당 산정서(1505함).xlsx
+++ b/overtime/sample/5월 초과근무수당 산정서(1505함).xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO34"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,659 +547,816 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>김근홍</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>급여 세부내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>근무시간(시간)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>총 근무시간</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>총 복무규정시간</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="E13" t="inlineStr">
         <is>
-          <t>복무규정시간(시간)</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
+          <t>근무시간(시간)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK13" t="n">
         <v>220</v>
       </c>
-      <c r="AO13" t="n">
-        <v>120</v>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>총 근무시간</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>총 복무규정시간</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="E14" t="inlineStr">
         <is>
-          <t>시간외(시간)</t>
-        </is>
-      </c>
-      <c r="AK14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>시간외(시간)</t>
-        </is>
+          <t>복무규정시간(시간)</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>220</v>
       </c>
       <c r="AO14" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="E15" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
-        </is>
+          <t>시간외(시간)</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>100</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
+          <t>시간외(시간)</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="E16" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
       <c r="E17" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" t="inlineStr">
         <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AO18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
           <t>교대시간(분)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="20">
+      <c r="A20" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>최영필</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>급여 세부내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>근무시간(시간)</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>8</v>
-      </c>
-      <c r="I20" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>8</v>
-      </c>
-      <c r="S20" t="n">
-        <v>8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>8</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>8</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>232</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>총 근무시간</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>총 복무규정시간</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="E21" t="inlineStr">
         <is>
-          <t>복무규정시간(시간)</t>
-        </is>
-      </c>
-      <c r="AN21" t="n">
+          <t>근무시간(시간)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>8</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK21" t="n">
         <v>232</v>
       </c>
-      <c r="AO21" t="n">
-        <v>120</v>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>총 근무시간</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>총 복무규정시간</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="E22" t="inlineStr">
         <is>
-          <t>시간외(시간)</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>시간외(시간)</t>
-        </is>
+          <t>복무규정시간(시간)</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>232</v>
       </c>
       <c r="AO22" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23">
       <c r="E23" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
-        </is>
+          <t>시간외(시간)</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>100</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
+          <t>시간외(시간)</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="E24" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="E25" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="E26" t="inlineStr">
         <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
           <t>교대시간(분)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="28">
+      <c r="A28" t="n">
         <v>3</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>현관용</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t>급여 세부내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>근무시간(시간)</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>8</v>
-      </c>
-      <c r="G28" t="n">
-        <v>8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" t="n">
-        <v>8</v>
-      </c>
-      <c r="K28" t="n">
-        <v>8</v>
-      </c>
-      <c r="L28" t="n">
-        <v>8</v>
-      </c>
-      <c r="M28" t="n">
-        <v>8</v>
-      </c>
-      <c r="N28" t="n">
-        <v>8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>8</v>
-      </c>
-      <c r="S28" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
-      </c>
-      <c r="U28" t="n">
-        <v>8</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>208</v>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>총 근무시간</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>총 복무규정시간</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="E29" t="inlineStr">
         <is>
-          <t>복무규정시간(시간)</t>
-        </is>
-      </c>
-      <c r="AN29" t="n">
+          <t>근무시간(시간)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>8</v>
+      </c>
+      <c r="V29" t="n">
+        <v>8</v>
+      </c>
+      <c r="W29" t="n">
+        <v>8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK29" t="n">
         <v>208</v>
       </c>
-      <c r="AO29" t="n">
-        <v>120</v>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>총 근무시간</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>총 복무규정시간</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="E30" t="inlineStr">
         <is>
-          <t>시간외(시간)</t>
-        </is>
-      </c>
-      <c r="AK30" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>시간외(시간)</t>
-        </is>
+          <t>복무규정시간(시간)</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>208</v>
       </c>
       <c r="AO30" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31">
       <c r="E31" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
-        </is>
+          <t>시간외(시간)</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>108</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>야간(시간)</t>
+          <t>시간외(시간)</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="E32" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>휴일(일수)</t>
+          <t>야간(시간)</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="E33" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>출동가산(일수)</t>
+          <t>휴일(일수)</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="E34" t="inlineStr">
         <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>출동가산(일수)</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="inlineStr">
+        <is>
           <t>교대시간(분)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="AN11:AO11"/>
+    <mergeCell ref="AN12:AO12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="AN27:AO27"/>
-    <mergeCell ref="AN19:AO19"/>
+    <mergeCell ref="AN28:AO28"/>
+    <mergeCell ref="AN20:AO20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1228,6 +1385,121 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>14</v>
+      </c>
+      <c r="T10" t="n">
+        <v>15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>16</v>
+      </c>
+      <c r="V10" t="n">
+        <v>17</v>
+      </c>
+      <c r="W10" t="n">
+        <v>18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="n">
         <v>1</v>
@@ -1242,6 +1514,161 @@
           <t>구분</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
       <c r="AN11" t="inlineStr">
         <is>
           <t>급여 세부내용</t>
@@ -1445,8 +1872,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="AN11:AO11"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
